--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20241.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="139">
   <si>
     <t>Mat</t>
   </si>
@@ -85,99 +85,111 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>JALAPA</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>OREA</t>
   </si>
   <si>
     <t>PALMA</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>CRESCENCIO</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>TOLEDO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JALAPA</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
     <t>PELLICO</t>
   </si>
   <si>
@@ -187,82 +199,91 @@
     <t>ZAVALA</t>
   </si>
   <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>MORA</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
     <t>RANGEL</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
   </si>
   <si>
     <t>CIRUELO</t>
@@ -277,27 +298,93 @@
     <t>DELGADO</t>
   </si>
   <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
     <t>CRISTHIAN</t>
   </si>
   <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>AZURA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
+    <t>GABAEL</t>
+  </si>
+  <si>
+    <t>SHERLIN</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>BARUCH BOSET</t>
+  </si>
+  <si>
+    <t>AHILY</t>
+  </si>
+  <si>
+    <t>ISAAC ASAEL</t>
+  </si>
+  <si>
+    <t>CALEB ELI</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>LUIS FELIPE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
   </si>
   <si>
     <t>CLAUDIA PAOLA</t>
   </si>
   <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
     <t>EDUARDO</t>
   </si>
   <si>
@@ -307,76 +394,31 @@
     <t>DANA PAOLA</t>
   </si>
   <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
     <t>ROBERTO</t>
   </si>
   <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
     <t>GEOVANNI</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>BARUCH BOSET</t>
-  </si>
-  <si>
-    <t>AHILY</t>
-  </si>
-  <si>
-    <t>ANA SHECIT</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
-  </si>
-  <si>
-    <t>BRENDA JANELY</t>
-  </si>
-  <si>
-    <t>ISAAC ASAEL</t>
-  </si>
-  <si>
-    <t>CALEB ELI</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
   </si>
   <si>
     <t>LUISA MARIA</t>
@@ -948,10 +990,10 @@
         <v>28</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8">
         <v>18</v>
@@ -960,7 +1002,7 @@
         <v>64.29000000000001</v>
       </c>
       <c r="H8">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -1151,16 +1193,19 @@
         <v>28</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>78.56999999999999</v>
+      </c>
+      <c r="H8">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -1369,19 +1414,19 @@
         <v>28</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G8">
-        <v>64.29000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H8">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1391,7 +1436,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1423,16 +1468,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920013</v>
+        <v>22330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1446,16 +1491,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920015</v>
+        <v>22330051920006</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1469,22 +1514,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920231</v>
+        <v>22330051920015</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1492,22 +1537,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920230</v>
+        <v>22330051920017</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1515,22 +1560,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920153</v>
+        <v>22330051920382</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1538,22 +1583,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920386</v>
+        <v>22330051920098</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1561,22 +1606,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920212</v>
+        <v>22330051920116</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1584,22 +1629,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920359</v>
+        <v>22330051920231</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1607,22 +1652,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920237</v>
+        <v>22330051920369</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1630,22 +1675,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920071</v>
+        <v>22330051920366</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1653,22 +1698,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920053</v>
+        <v>22330051920386</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1676,22 +1721,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920242</v>
+        <v>22330051920189</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1699,16 +1744,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920033</v>
+        <v>22330051920043</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1722,16 +1767,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920051</v>
+        <v>22330051920045</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1745,16 +1790,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920003</v>
+        <v>22330051920013</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1774,10 +1819,10 @@
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1797,10 +1842,10 @@
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1814,16 +1859,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920098</v>
+        <v>22330051920339</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1837,16 +1882,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920339</v>
+        <v>22330051920340</v>
       </c>
       <c r="B20" t="s">
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1860,16 +1905,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920340</v>
+        <v>22330051920108</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1883,16 +1928,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920108</v>
+        <v>22330051920107</v>
       </c>
       <c r="B22" t="s">
         <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1906,22 +1951,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920107</v>
+        <v>22330051920151</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1929,22 +1974,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920234</v>
+        <v>22330051920174</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1952,22 +1997,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920401</v>
+        <v>22330051920333</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1975,22 +2020,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920259</v>
+        <v>22330051920053</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1998,22 +2043,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920151</v>
+        <v>22330051920054</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2021,22 +2066,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920174</v>
+        <v>22330051920061</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2044,16 +2089,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920333</v>
+        <v>22330051920212</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2067,16 +2112,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920053</v>
+        <v>22330051920064</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2090,16 +2135,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920054</v>
+        <v>21330051920359</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2113,16 +2158,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920061</v>
+        <v>21330051920237</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2136,16 +2181,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920064</v>
+        <v>22330051920071</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2162,13 +2207,13 @@
         <v>22330051920218</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2182,16 +2227,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920084</v>
+        <v>21330051920053</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2205,22 +2250,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920246</v>
+        <v>21330051920242</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2228,22 +2273,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>22330051920110</v>
+        <v>22330051920084</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D37" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2251,22 +2296,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>22330051920144</v>
+        <v>22330051920033</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2274,22 +2319,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>22330051920176</v>
+        <v>22330051920038</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
         <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2297,24 +2342,208 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>22330051920148</v>
+        <v>22330051920327</v>
       </c>
       <c r="B40" t="s">
         <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>22330051920048</v>
+      </c>
+      <c r="B41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" t="s">
+        <v>132</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>22330051920049</v>
+      </c>
+      <c r="B42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" t="s">
+        <v>93</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>22330051920051</v>
+      </c>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>22330051920246</v>
+      </c>
+      <c r="B44" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" t="s">
+        <v>134</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
         <v>14</v>
       </c>
-      <c r="G40">
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>22330051920110</v>
+      </c>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" t="s">
+        <v>135</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>22330051920144</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" t="s">
+        <v>136</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>22330051920176</v>
+      </c>
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" t="s">
+        <v>137</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>22330051920148</v>
+      </c>
+      <c r="B48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" t="s">
+        <v>138</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20241.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="138">
   <si>
     <t>Mat</t>
   </si>
@@ -64,9 +64,6 @@
     <t>5BLCM</t>
   </si>
   <si>
-    <t>5ALCV</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -106,144 +103,147 @@
     <t>ROJAS</t>
   </si>
   <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>JALAPA</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CRESCENCIO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>TOLEDO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZAVALA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>QUINTANA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>JALAPA</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>CRESCENCIO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>TOLEDO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZAVALA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
+    <t>PEÑA</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
     <t>CARRASCO</t>
   </si>
   <si>
@@ -319,49 +319,46 @@
     <t>ANDRES</t>
   </si>
   <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>AILYN</t>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>GABAEL</t>
+  </si>
+  <si>
+    <t>SHERLIN</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>BARUCH BOSET</t>
+  </si>
+  <si>
+    <t>AHILY</t>
+  </si>
+  <si>
+    <t>ISAAC ASAEL</t>
   </si>
   <si>
     <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>BARUCH BOSET</t>
-  </si>
-  <si>
-    <t>AHILY</t>
-  </si>
-  <si>
-    <t>ISAAC ASAEL</t>
   </si>
   <si>
     <t>CALEB ELI</t>
@@ -791,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -979,32 +976,6 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>28</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>18</v>
-      </c>
-      <c r="G8">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="H8">
-        <v>6.5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1012,7 +983,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1182,32 +1153,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>28</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="F8">
-        <v>22</v>
-      </c>
-      <c r="G8">
-        <v>78.56999999999999</v>
-      </c>
-      <c r="H8">
-        <v>6.5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1215,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1403,32 +1348,6 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>28</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="F8">
-        <v>22</v>
-      </c>
-      <c r="G8">
-        <v>78.56999999999999</v>
-      </c>
-      <c r="H8">
-        <v>7.1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1436,7 +1355,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1445,25 +1364,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1471,10 +1390,10 @@
         <v>22330051920003</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
         <v>93</v>
@@ -1494,10 +1413,10 @@
         <v>22330051920006</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
         <v>94</v>
@@ -1517,10 +1436,10 @@
         <v>22330051920015</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
         <v>95</v>
@@ -1540,10 +1459,10 @@
         <v>22330051920017</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
         <v>96</v>
@@ -1563,10 +1482,10 @@
         <v>22330051920382</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
         <v>97</v>
@@ -1586,10 +1505,10 @@
         <v>22330051920098</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
         <v>98</v>
@@ -1609,10 +1528,10 @@
         <v>22330051920116</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
         <v>99</v>
@@ -1629,13 +1548,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920231</v>
+        <v>22330051920153</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
         <v>100</v>
@@ -1644,7 +1563,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1652,13 +1571,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920369</v>
+        <v>22330051920426</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
         <v>101</v>
@@ -1667,7 +1586,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1675,13 +1594,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920366</v>
+        <v>22330051920189</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
         <v>102</v>
@@ -1690,7 +1609,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1698,13 +1617,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920386</v>
+        <v>22330051920043</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
         <v>103</v>
@@ -1713,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1721,13 +1640,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920189</v>
+        <v>22330051920045</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
         <v>104</v>
@@ -1744,13 +1663,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920043</v>
+        <v>22330051920013</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
         <v>105</v>
@@ -1759,21 +1678,21 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920045</v>
+        <v>22330051920320</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
         <v>106</v>
@@ -1782,21 +1701,21 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920013</v>
+        <v>22330051920322</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
         <v>107</v>
@@ -1813,13 +1732,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920320</v>
+        <v>22330051920339</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
         <v>108</v>
@@ -1828,7 +1747,7 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1836,10 +1755,10 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920322</v>
+        <v>22330051920340</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
         <v>71</v>
@@ -1851,7 +1770,7 @@
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1859,10 +1778,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920339</v>
+        <v>22330051920108</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
         <v>72</v>
@@ -1882,13 +1801,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920340</v>
+        <v>22330051920107</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
         <v>111</v>
@@ -1905,13 +1824,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920108</v>
+        <v>22330051920151</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
         <v>112</v>
@@ -1920,7 +1839,7 @@
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1928,13 +1847,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920107</v>
+        <v>22330051920386</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
         <v>113</v>
@@ -1943,7 +1862,7 @@
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1951,13 +1870,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920151</v>
+        <v>22330051920174</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
         <v>114</v>
@@ -1974,13 +1893,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920174</v>
+        <v>22330051920333</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>115</v>
@@ -1989,7 +1908,7 @@
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1997,13 +1916,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920333</v>
+        <v>22330051920053</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="D25" t="s">
         <v>116</v>
@@ -2020,13 +1939,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920053</v>
+        <v>22330051920054</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
         <v>117</v>
@@ -2043,13 +1962,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920054</v>
+        <v>22330051920061</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
         <v>118</v>
@@ -2066,13 +1985,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920061</v>
+        <v>22330051920212</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
         <v>119</v>
@@ -2089,13 +2008,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920212</v>
+        <v>22330051920064</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
         <v>120</v>
@@ -2112,13 +2031,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920064</v>
+        <v>21330051920359</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
         <v>121</v>
@@ -2135,10 +2054,10 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920359</v>
+        <v>21330051920237</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
         <v>26</v>
@@ -2158,13 +2077,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920237</v>
+        <v>22330051920071</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
         <v>123</v>
@@ -2181,13 +2100,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920071</v>
+        <v>22330051920218</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s">
         <v>124</v>
@@ -2204,13 +2123,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920218</v>
+        <v>21330051920053</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="D34" t="s">
         <v>125</v>
@@ -2227,13 +2146,13 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920053</v>
+        <v>21330051920242</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
         <v>126</v>
@@ -2250,13 +2169,13 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920242</v>
+        <v>22330051920084</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
         <v>127</v>
@@ -2273,13 +2192,13 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>22330051920084</v>
+        <v>22330051920033</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D37" t="s">
         <v>128</v>
@@ -2288,7 +2207,7 @@
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2296,13 +2215,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>22330051920033</v>
+        <v>22330051920038</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D38" t="s">
         <v>129</v>
@@ -2319,13 +2238,13 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>22330051920038</v>
+        <v>22330051920327</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D39" t="s">
         <v>130</v>
@@ -2342,13 +2261,13 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>22330051920327</v>
+        <v>22330051920048</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
         <v>131</v>
@@ -2365,16 +2284,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>22330051920048</v>
+        <v>22330051920049</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2388,16 +2307,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>22330051920049</v>
+        <v>22330051920051</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D42" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2411,13 +2330,13 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>22330051920051</v>
+        <v>22330051920246</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D43" t="s">
         <v>133</v>
@@ -2426,7 +2345,7 @@
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2434,13 +2353,13 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>22330051920246</v>
+        <v>22330051920110</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C44" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D44" t="s">
         <v>134</v>
@@ -2457,13 +2376,13 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>22330051920110</v>
+        <v>22330051920144</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D45" t="s">
         <v>135</v>
@@ -2480,13 +2399,13 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>22330051920144</v>
+        <v>22330051920176</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
         <v>136</v>
@@ -2503,13 +2422,13 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>22330051920176</v>
+        <v>22330051920148</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="D47" t="s">
         <v>137</v>
@@ -2521,29 +2440,6 @@
         <v>14</v>
       </c>
       <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>22330051920148</v>
-      </c>
-      <c r="B48" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" t="s">
-        <v>138</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>14</v>
-      </c>
-      <c r="G48">
         <v>1</v>
       </c>
     </row>
